--- a/data_lake/datos_diarios_preliminares/dt=2026-07-30/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-30/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEB6582-8ADF-469A-97B0-9FCF0C84C932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ABFE9E-C7F3-448E-AE03-A29A10A40835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AL$1:$AL$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AM$1:$AM$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6354,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="115" width="32.42578125" style="50" customWidth="1"/>
-    <col min="116" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="116" width="32.42578125" style="50" customWidth="1"/>
+    <col min="117" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6722,16 +6722,18 @@
       <c r="AL5" s="56">
         <v>27.6</v>
       </c>
-      <c r="AM5" s="56"/>
+      <c r="AM5" s="56">
+        <v>29.7</v>
+      </c>
       <c r="AN5" s="56"/>
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.796428571428571</v>
+        <v>28.827586206896552</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6739,7 +6741,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.64321368245730071</v>
+        <v>0.67437131792528149</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6857,16 +6859,18 @@
       <c r="AL6" s="56">
         <v>27.6</v>
       </c>
-      <c r="AM6" s="56"/>
+      <c r="AM6" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AN6" s="56"/>
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.807142857142857</v>
+        <v>28.806896551724137</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6874,7 +6878,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.41190896819403733</v>
+        <v>0.41166266277531705</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6992,16 +6996,18 @@
       <c r="AL7" s="56">
         <v>30.9</v>
       </c>
-      <c r="AM7" s="56"/>
+      <c r="AM7" s="56">
+        <v>32</v>
+      </c>
       <c r="AN7" s="56"/>
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.392857142857142</v>
+        <v>31.413793103448278</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7009,7 +7015,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.1926766513056819</v>
+        <v>2.2136126118968171</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7127,16 +7133,18 @@
       <c r="AL8" s="56">
         <v>30.3</v>
       </c>
-      <c r="AM8" s="56"/>
+      <c r="AM8" s="56">
+        <v>30.9</v>
+      </c>
       <c r="AN8" s="56"/>
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.685714285714287</v>
+        <v>29.727586206896554</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7144,7 +7152,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1071749695428856</v>
+        <v>1.1490468907251525</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7262,16 +7270,18 @@
       <c r="AL9" s="56">
         <v>30.8</v>
       </c>
-      <c r="AM9" s="56"/>
+      <c r="AM9" s="56">
+        <v>30.9</v>
+      </c>
       <c r="AN9" s="56"/>
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.371428571428574</v>
+        <v>29.424137931034487</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7279,7 +7289,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.41604041120165647</v>
+        <v>-0.3633310515957433</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7397,16 +7407,18 @@
       <c r="AL10" s="56">
         <v>31.5</v>
       </c>
-      <c r="AM10" s="56"/>
+      <c r="AM10" s="56">
+        <v>33</v>
+      </c>
       <c r="AN10" s="56"/>
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.582142857142856</v>
+        <v>31.631034482758619</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7414,7 +7426,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.5027208227377962</v>
+        <v>1.5516124483535592</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7532,16 +7544,18 @@
       <c r="AL11" s="56">
         <v>33.5</v>
       </c>
-      <c r="AM11" s="56"/>
+      <c r="AM11" s="56">
+        <v>34.4</v>
+      </c>
       <c r="AN11" s="56"/>
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.564285714285717</v>
+        <v>32.627586206896552</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7549,7 +7563,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>2.560371637057866</v>
+        <v>2.6236721296687016</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7667,16 +7681,18 @@
       <c r="AL12" s="56">
         <v>30.1</v>
       </c>
-      <c r="AM12" s="56"/>
+      <c r="AM12" s="56">
+        <v>31</v>
+      </c>
       <c r="AN12" s="56"/>
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>29.985714285714277</v>
+        <v>30.020689655172408</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7684,7 +7700,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7200478963986967</v>
+        <v>1.7550232658568277</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7802,16 +7818,18 @@
       <c r="AL13" s="56">
         <v>31.2</v>
       </c>
-      <c r="AM13" s="56"/>
+      <c r="AM13" s="56">
+        <v>31.4</v>
+      </c>
       <c r="AN13" s="56"/>
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>29.94285714285714</v>
+        <v>29.993103448275857</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7819,7 +7837,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.6134624450447781</v>
+        <v>1.6637087504634955</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7937,16 +7955,18 @@
       <c r="AL14" s="56">
         <v>24.5</v>
       </c>
-      <c r="AM14" s="56"/>
+      <c r="AM14" s="56">
+        <v>25</v>
+      </c>
       <c r="AN14" s="56"/>
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.61785714285714</v>
+        <v>23.665517241379309</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7954,7 +7974,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.8963171189622905</v>
+        <v>1.9439772174844592</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8072,16 +8092,18 @@
       <c r="AL15" s="56">
         <v>31.4</v>
       </c>
-      <c r="AM15" s="56"/>
+      <c r="AM15" s="56">
+        <v>31.5</v>
+      </c>
       <c r="AN15" s="56"/>
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.260714285714283</v>
+        <v>29.337931034482757</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8089,7 +8111,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>1.0252089093702033</v>
+        <v>1.102425658138678</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8207,16 +8229,18 @@
       <c r="AL16" s="56">
         <v>28.7</v>
       </c>
-      <c r="AM16" s="56"/>
+      <c r="AM16" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AN16" s="56"/>
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.371428571428574</v>
+        <v>28.413793103448281</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8224,7 +8248,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.73377572302559457</v>
+        <v>0.77614025504530204</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8342,16 +8366,18 @@
       <c r="AL17" s="56">
         <v>25.7</v>
       </c>
-      <c r="AM17" s="56"/>
+      <c r="AM17" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AN17" s="56"/>
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.632142857142863</v>
+        <v>24.689655172413797</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8359,7 +8385,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.64851918798666475</v>
+        <v>0.70603150325759856</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8477,16 +8503,18 @@
       <c r="AL18" s="56">
         <v>19.3</v>
       </c>
-      <c r="AM18" s="56"/>
+      <c r="AM18" s="56">
+        <v>19.7</v>
+      </c>
       <c r="AN18" s="56"/>
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.771428571428572</v>
+        <v>18.80344827586207</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8494,7 +8522,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.3530773169482906</v>
+        <v>1.3850970213817888</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8612,16 +8640,18 @@
       <c r="AL19" s="56">
         <v>25.5</v>
       </c>
-      <c r="AM19" s="56"/>
+      <c r="AM19" s="56">
+        <v>25.3</v>
+      </c>
       <c r="AN19" s="56"/>
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.228571428571428</v>
+        <v>24.265517241379307</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8629,7 +8659,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.0950364823348764</v>
+        <v>2.1319822951427554</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8747,16 +8777,18 @@
       <c r="AL20" s="56">
         <v>25.8</v>
       </c>
-      <c r="AM20" s="56"/>
+      <c r="AM20" s="56">
+        <v>25</v>
+      </c>
       <c r="AN20" s="56"/>
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.296428571428567</v>
+        <v>24.320689655172409</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8764,7 +8796,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.6887631454566971</v>
+        <v>1.7130242292005384</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8882,16 +8914,18 @@
       <c r="AL21" s="56">
         <v>28.1</v>
       </c>
-      <c r="AM21" s="56"/>
+      <c r="AM21" s="56">
+        <v>27</v>
+      </c>
       <c r="AN21" s="56"/>
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.157142857142855</v>
+        <v>27.151724137931033</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8899,7 +8933,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.4670609653857234</v>
+        <v>2.461642246173902</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9017,16 +9051,18 @@
       <c r="AL22" s="56">
         <v>15.5</v>
       </c>
-      <c r="AM22" s="56"/>
+      <c r="AM22" s="56">
+        <v>16.2</v>
+      </c>
       <c r="AN22" s="56"/>
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.482142857142858</v>
+        <v>15.506896551724138</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9034,7 +9070,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.701809937374458</v>
+        <v>1.726563631955738</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9152,16 +9188,18 @@
       <c r="AL23" s="56">
         <v>26.5</v>
       </c>
-      <c r="AM23" s="56"/>
+      <c r="AM23" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AN23" s="56"/>
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.074999999999996</v>
+        <v>26.082758620689649</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9287,16 +9325,18 @@
       <c r="AL24" s="56">
         <v>30.6</v>
       </c>
-      <c r="AM24" s="56"/>
+      <c r="AM24" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AN24" s="56"/>
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.442857142857147</v>
+        <v>29.479310344827589</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9304,7 +9344,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.0804986581210265</v>
+        <v>1.1169518600914685</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9422,16 +9462,18 @@
       <c r="AL25" s="56">
         <v>22.1</v>
       </c>
-      <c r="AM25" s="56"/>
+      <c r="AM25" s="56">
+        <v>21.7</v>
+      </c>
       <c r="AN25" s="56"/>
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>21.849999999999998</v>
+        <v>21.844827586206897</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9439,7 +9481,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.9165755437977978</v>
+        <v>1.9114031300046967</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9557,16 +9599,18 @@
       <c r="AL26" s="56">
         <v>11.1</v>
       </c>
-      <c r="AM26" s="56"/>
+      <c r="AM26" s="56">
+        <v>9.4</v>
+      </c>
       <c r="AN26" s="56"/>
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.517857142857141</v>
+        <v>11.444827586206895</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9574,7 +9618,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.1475422427035511</v>
+        <v>1.0745126860533052</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9692,16 +9736,18 @@
       <c r="AL27" s="56">
         <v>29.1</v>
       </c>
-      <c r="AM27" s="56"/>
+      <c r="AM27" s="56">
+        <v>30.1</v>
+      </c>
       <c r="AN27" s="56"/>
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.078571428571433</v>
+        <v>28.148275862068971</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9709,7 +9755,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.0898654589755843</v>
+        <v>1.1595698924731224</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9827,16 +9873,18 @@
       <c r="AL28" s="56">
         <v>28.9</v>
       </c>
-      <c r="AM28" s="56"/>
+      <c r="AM28" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AN28" s="56"/>
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.596428571428572</v>
+        <v>26.617241379310347</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9844,7 +9892,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.84501001995162994</v>
+        <v>0.86582282783340503</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9962,16 +10010,18 @@
       <c r="AL29" s="56">
         <v>28.9</v>
       </c>
-      <c r="AM29" s="56"/>
+      <c r="AM29" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AN29" s="56"/>
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.75714285714286</v>
+        <v>27.80344827586207</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9979,7 +10029,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.80310064288562089</v>
+        <v>0.84940606160483156</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10097,16 +10147,18 @@
       <c r="AL30" s="56">
         <v>26.9</v>
       </c>
-      <c r="AM30" s="56"/>
+      <c r="AM30" s="56">
+        <v>23.3</v>
+      </c>
       <c r="AN30" s="56"/>
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.357142857142858</v>
+        <v>25.286206896551722</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10114,7 +10166,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.83914137401348654</v>
+        <v>0.7682054134223506</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -10232,16 +10284,18 @@
       <c r="AL31" s="98">
         <v>27.4</v>
       </c>
-      <c r="AM31" s="98"/>
+      <c r="AM31" s="98">
+        <v>28</v>
+      </c>
       <c r="AN31" s="98"/>
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.803571428571427</v>
+        <v>26.844827586206897</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10249,7 +10303,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4346228025260288</v>
+        <v>1.4758789601614986</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10367,16 +10421,18 @@
       <c r="AL32" s="56">
         <v>20.2</v>
       </c>
-      <c r="AM32" s="56"/>
+      <c r="AM32" s="56">
+        <v>20.266666666666669</v>
+      </c>
       <c r="AN32" s="56"/>
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.448809523809526</v>
+        <v>20.442528735632184</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10384,7 +10440,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.7919534717006869</v>
+        <v>2.7856726835233445</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10502,16 +10558,18 @@
       <c r="AL33" s="56">
         <v>28.65</v>
       </c>
-      <c r="AM33" s="56"/>
+      <c r="AM33" s="56">
+        <v>29</v>
+      </c>
       <c r="AN33" s="56"/>
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>27.933928571428574</v>
+        <v>27.970689655172418</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10519,7 +10577,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.1064564902160221</v>
+        <v>1.1432175739598662</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10637,16 +10695,18 @@
       <c r="AL34" s="56">
         <v>21.6</v>
       </c>
-      <c r="AM34" s="56"/>
+      <c r="AM34" s="56">
+        <v>22.333333333333329</v>
+      </c>
       <c r="AN34" s="56"/>
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.292857142857144</v>
+        <v>21.328735632183911</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10654,7 +10714,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.5056595511768229</v>
+        <v>1.541538040503589</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10772,16 +10832,18 @@
       <c r="AL35" s="56">
         <v>24.8</v>
       </c>
-      <c r="AM35" s="56"/>
+      <c r="AM35" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AN35" s="56"/>
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.533928571428568</v>
+        <v>24.553448275862067</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10789,7 +10851,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.49568067171116681</v>
+        <v>0.51520037614466574</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10907,16 +10969,18 @@
       <c r="AL36" s="56">
         <v>19.7</v>
       </c>
-      <c r="AM36" s="56"/>
+      <c r="AM36" s="56">
+        <v>19.7</v>
+      </c>
       <c r="AN36" s="56"/>
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>19.976785714285715</v>
+        <v>19.967241379310348</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10924,7 +10988,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>0.97797465106732417</v>
+        <v>0.96843031609195762</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11042,16 +11106,18 @@
       <c r="AL37" s="56">
         <v>27.4</v>
       </c>
-      <c r="AM37" s="56"/>
+      <c r="AM37" s="56">
+        <v>27.55</v>
+      </c>
       <c r="AN37" s="56"/>
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.369642857142857</v>
+        <v>27.375862068965517</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11059,7 +11125,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.4834129832054757</v>
+        <v>1.4896321950281362</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11173,16 +11239,18 @@
       <c r="AL38" s="56">
         <v>15.55</v>
       </c>
-      <c r="AM38" s="56"/>
+      <c r="AM38" s="56">
+        <v>16.600000000000001</v>
+      </c>
       <c r="AN38" s="56"/>
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>15.890384615384615</v>
+        <v>15.916666666666666</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11190,7 +11258,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>0.87245560843393477</v>
+        <v>0.89873765971598552</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11303,17 +11371,21 @@
       <c r="AK39" s="56">
         <v>21.06666666666667</v>
       </c>
-      <c r="AL39" s="56"/>
-      <c r="AM39" s="56"/>
+      <c r="AL39" s="56">
+        <v>22.666666666666671</v>
+      </c>
+      <c r="AM39" s="56">
+        <v>23</v>
+      </c>
       <c r="AN39" s="56"/>
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.215384615384615</v>
+        <v>22.259523809523809</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11427,16 +11499,18 @@
       <c r="AL40" s="56">
         <v>25.13333333333334</v>
       </c>
-      <c r="AM40" s="56"/>
+      <c r="AM40" s="56">
+        <v>25.93333333333333</v>
+      </c>
       <c r="AN40" s="56"/>
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.191666666666663</v>
+        <v>25.223913043478255</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11444,7 +11518,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.3398759182396915</v>
+        <v>2.3721222950512839</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11560,16 +11634,18 @@
       <c r="AL41" s="56">
         <v>19</v>
       </c>
-      <c r="AM41" s="56"/>
+      <c r="AM41" s="56">
+        <v>20.733333333333331</v>
+      </c>
       <c r="AN41" s="56"/>
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.058024691358018</v>
+        <v>20.082142857142852</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11577,7 +11653,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>1.5659155000302789</v>
+        <v>1.5900336658151133</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11695,16 +11771,18 @@
       <c r="AL42" s="56">
         <v>27.65</v>
       </c>
-      <c r="AM42" s="56"/>
+      <c r="AM42" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AN42" s="56"/>
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.936607142857138</v>
+        <v>27.969827586206893</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11712,7 +11790,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.18392162579886673</v>
+        <v>0.21714206914862189</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11826,16 +11904,18 @@
       <c r="AL43" s="56">
         <v>28.9</v>
       </c>
-      <c r="AM43" s="56"/>
+      <c r="AM43" s="56">
+        <v>30.35</v>
+      </c>
       <c r="AN43" s="56"/>
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.25961538461539</v>
+        <v>29.300000000000004</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11961,16 +12041,18 @@
       <c r="AL44" s="56">
         <v>28.75</v>
       </c>
-      <c r="AM44" s="56"/>
+      <c r="AM44" s="56">
+        <v>28.75</v>
+      </c>
       <c r="AN44" s="56"/>
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.512499999999996</v>
+        <v>28.520689655172411</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11978,7 +12060,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.170156555717174</v>
+        <v>1.1783462108895897</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12096,16 +12178,18 @@
       <c r="AL45" s="56">
         <v>29.2</v>
       </c>
-      <c r="AM45" s="56"/>
+      <c r="AM45" s="56">
+        <v>29.4</v>
+      </c>
       <c r="AN45" s="56"/>
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.166071428571435</v>
+        <v>29.17413793103449</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12113,7 +12197,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.397963953640005</v>
+        <v>1.4060304561030605</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12231,16 +12315,18 @@
       <c r="AL46" s="56">
         <v>28.75</v>
       </c>
-      <c r="AM46" s="56"/>
+      <c r="AM46" s="56">
+        <v>29.7</v>
+      </c>
       <c r="AN46" s="56"/>
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>28.879464285714285</v>
+        <v>28.907758620689656</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12248,7 +12334,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>0.97326665381680399</v>
+        <v>1.0015609887921748</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12366,16 +12452,18 @@
       <c r="AL47" s="56">
         <v>30.6</v>
       </c>
-      <c r="AM47" s="56"/>
+      <c r="AM47" s="56">
+        <v>31.333333333333329</v>
+      </c>
       <c r="AN47" s="56"/>
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ47" s="71">
         <f t="shared" si="1"/>
-        <v>29.894047619047626</v>
+        <v>29.94367816091955</v>
       </c>
       <c r="AR47" s="71">
         <f>IFERROR(VLOOKUP(A47,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12383,7 +12471,7 @@
       </c>
       <c r="AS47" s="71">
         <f t="shared" si="2"/>
-        <v>1.9251717597302367</v>
+        <v>1.9748023016021605</v>
       </c>
     </row>
     <row r="48" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12659,16 +12747,18 @@
       <c r="AL50" s="56">
         <v>29.8</v>
       </c>
-      <c r="AM50" s="56"/>
+      <c r="AM50" s="56">
+        <v>29.45</v>
+      </c>
       <c r="AN50" s="56"/>
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>29.205357142857139</v>
+        <v>29.213793103448275</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12676,7 +12766,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>1.9166667968253179</v>
+        <v>1.9251027574164539</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12980,16 +13070,18 @@
       <c r="AL53" s="56">
         <v>29</v>
       </c>
-      <c r="AM53" s="56"/>
+      <c r="AM53" s="56">
+        <v>29.35</v>
+      </c>
       <c r="AN53" s="56"/>
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>28.823214285714283</v>
+        <v>28.841379310344827</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12997,7 +13089,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.4639679891237343</v>
+        <v>1.4821330137542787</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13115,16 +13207,18 @@
       <c r="AL54" s="56">
         <v>29.85</v>
       </c>
-      <c r="AM54" s="56"/>
+      <c r="AM54" s="56">
+        <v>30.75</v>
+      </c>
       <c r="AN54" s="56"/>
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>29.976785714285722</v>
+        <v>30.003448275862077</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13132,7 +13226,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.4785596892193027</v>
+        <v>1.5052222507956579</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13236,16 +13330,18 @@
       <c r="AL55" s="56">
         <v>30.7</v>
       </c>
-      <c r="AM55" s="56"/>
+      <c r="AM55" s="56">
+        <v>30.7</v>
+      </c>
       <c r="AN55" s="56"/>
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v>30.169047619047628</v>
+        <v>30.193181818181827</v>
       </c>
       <c r="AR55" s="71">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13253,7 +13349,7 @@
       </c>
       <c r="AS55" s="71">
         <f t="shared" si="2"/>
-        <v>1.7380879488105876</v>
+        <v>1.7622221479447866</v>
       </c>
     </row>
     <row r="56" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13371,16 +13467,18 @@
       <c r="AL56" s="56">
         <v>28.65</v>
       </c>
-      <c r="AM56" s="56"/>
+      <c r="AM56" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AN56" s="56"/>
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ56" s="71">
         <f t="shared" si="1"/>
-        <v>29.289285714285715</v>
+        <v>29.275862068965516</v>
       </c>
       <c r="AR56" s="71" t="str">
         <f>IFERROR(VLOOKUP(A56,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13662,16 +13760,18 @@
       <c r="AL59" s="56">
         <v>30</v>
       </c>
-      <c r="AM59" s="56"/>
+      <c r="AM59" s="56">
+        <v>29.55</v>
+      </c>
       <c r="AN59" s="56"/>
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>29.041666666666668</v>
+        <v>29.059821428571428</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13679,7 +13779,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>0.92744683758450819</v>
+        <v>0.94560159948926881</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13922,16 +14022,18 @@
       <c r="AL61" s="56">
         <v>28.25</v>
       </c>
-      <c r="AM61" s="56"/>
+      <c r="AM61" s="56">
+        <v>27.85</v>
+      </c>
       <c r="AN61" s="56"/>
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>26.75178571428572</v>
+        <v>26.789655172413799</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13939,7 +14041,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>1.0451140325597592</v>
+        <v>1.0829834906878375</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14057,16 +14159,18 @@
       <c r="AL62" s="56">
         <v>28.4</v>
       </c>
-      <c r="AM62" s="56"/>
+      <c r="AM62" s="56">
+        <v>27.066666666666659</v>
+      </c>
       <c r="AN62" s="56"/>
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>26.045238095238098</v>
+        <v>26.080459770114945</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14074,7 +14178,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.5062341552742069</v>
+        <v>1.5414558301510546</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14332,16 +14436,18 @@
       <c r="AL65" s="56">
         <v>26.1</v>
       </c>
-      <c r="AM65" s="56"/>
+      <c r="AM65" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AN65" s="56"/>
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>25.757894736842111</v>
+        <v>25.815000000000005</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14349,7 +14455,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.75268877853095262</v>
+        <v>0.80979404168884628</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14467,16 +14573,18 @@
       <c r="AL66" s="56">
         <v>27.3</v>
       </c>
-      <c r="AM66" s="56"/>
+      <c r="AM66" s="56">
+        <v>27</v>
+      </c>
       <c r="AN66" s="56"/>
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.74821428571428</v>
+        <v>25.791379310344823</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14484,7 +14592,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.83909945543528863</v>
+        <v>0.88226448006583169</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14598,16 +14706,18 @@
       <c r="AL67" s="56">
         <v>27.65</v>
       </c>
-      <c r="AM67" s="56"/>
+      <c r="AM67" s="56">
+        <v>24.3</v>
+      </c>
       <c r="AN67" s="56"/>
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.619230769230764</v>
+        <v>25.570370370370366</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14615,7 +14725,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.96802385739955454</v>
+        <v>0.91916345853915615</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14733,16 +14843,18 @@
       <c r="AL68" s="56">
         <v>27.15</v>
       </c>
-      <c r="AM68" s="56"/>
+      <c r="AM68" s="56">
+        <v>23.9</v>
+      </c>
       <c r="AN68" s="56"/>
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.591071428571428</v>
+        <v>25.532758620689652</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14750,7 +14862,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>1.0659839258284087</v>
+        <v>1.0076711179466322</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14868,16 +14980,18 @@
       <c r="AL69" s="56">
         <v>25.95</v>
       </c>
-      <c r="AM69" s="56"/>
+      <c r="AM69" s="56">
+        <v>24.15</v>
+      </c>
       <c r="AN69" s="56"/>
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>24.997321428571436</v>
+        <v>24.968103448275869</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14885,7 +14999,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.67492374193942695</v>
+        <v>0.6457057616438604</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14989,16 +15103,18 @@
       <c r="AL70" s="56">
         <v>28</v>
       </c>
-      <c r="AM70" s="56"/>
+      <c r="AM70" s="56">
+        <v>26.733333333333331</v>
+      </c>
       <c r="AN70" s="56"/>
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>26.576190476190476</v>
+        <v>26.583333333333336</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15006,7 +15122,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>1.0062317851472748</v>
+        <v>1.0133746422901346</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15124,16 +15240,18 @@
       <c r="AL71" s="56">
         <v>27.5</v>
       </c>
-      <c r="AM71" s="56"/>
+      <c r="AM71" s="56">
+        <v>26.233333333333331</v>
+      </c>
       <c r="AN71" s="56"/>
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.982142857142858</v>
+        <v>25.99080459770115</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15141,7 +15259,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.31969994348932929</v>
+        <v>0.32836168404762134</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15257,16 +15375,18 @@
       <c r="AL72" s="56">
         <v>24.166666666666671</v>
       </c>
-      <c r="AM72" s="56"/>
+      <c r="AM72" s="56">
+        <v>25.3</v>
+      </c>
       <c r="AN72" s="56"/>
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>25.404938271604941</v>
+        <v>25.401190476190475</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15274,7 +15394,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.43172952864540193</v>
+        <v>0.42798173323093636</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15376,16 +15496,18 @@
       <c r="AL73" s="56">
         <v>27.3</v>
       </c>
-      <c r="AM73" s="56"/>
+      <c r="AM73" s="56">
+        <v>24.05</v>
+      </c>
       <c r="AN73" s="56"/>
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>25.862500000000001</v>
+        <v>25.776190476190475</v>
       </c>
       <c r="AR73" s="71" t="str">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15511,16 +15633,18 @@
       <c r="AL74" s="56">
         <v>23.175000000000001</v>
       </c>
-      <c r="AM74" s="56"/>
+      <c r="AM74" s="56">
+        <v>21.3</v>
+      </c>
       <c r="AN74" s="56"/>
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>20.920535714285712</v>
+        <v>20.933620689655172</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15528,7 +15652,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.92203696492560283</v>
+        <v>0.9351219402950619</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15646,16 +15770,18 @@
       <c r="AL75" s="56">
         <v>16.466666666666669</v>
       </c>
-      <c r="AM75" s="56"/>
+      <c r="AM75" s="56">
+        <v>16.466666666666669</v>
+      </c>
       <c r="AN75" s="56"/>
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>15.853571428571424</v>
+        <v>15.874712643678157</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15663,7 +15789,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.67252773660463383</v>
+        <v>0.69366895171136633</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15781,16 +15907,18 @@
       <c r="AL76" s="56">
         <v>21.6</v>
       </c>
-      <c r="AM76" s="56"/>
+      <c r="AM76" s="56">
+        <v>21.9</v>
+      </c>
       <c r="AN76" s="56"/>
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>20.727678571428573</v>
+        <v>20.768103448275863</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15798,7 +15926,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>0.92771195990235356</v>
+        <v>0.96813683674964324</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15916,16 +16044,18 @@
       <c r="AL77" s="56">
         <v>25.4</v>
       </c>
-      <c r="AM77" s="56"/>
+      <c r="AM77" s="56">
+        <v>23.866666666666671</v>
+      </c>
       <c r="AN77" s="56"/>
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>24.026190476190468</v>
+        <v>24.020689655172408</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15933,7 +16063,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.3429496202115487</v>
+        <v>1.3374487991934885</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16051,16 +16181,18 @@
       <c r="AL78" s="56">
         <v>31.85</v>
       </c>
-      <c r="AM78" s="56"/>
+      <c r="AM78" s="56">
+        <v>32.5</v>
+      </c>
       <c r="AN78" s="56"/>
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>31.1875</v>
+        <v>31.232758620689655</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16068,7 +16200,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>2.003570189477351</v>
+        <v>2.0488288101670058</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16182,16 +16314,18 @@
       <c r="AL79" s="56">
         <v>32.6</v>
       </c>
-      <c r="AM79" s="56"/>
+      <c r="AM79" s="56">
+        <v>32.133333333333333</v>
+      </c>
       <c r="AN79" s="56"/>
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.297435897435893</v>
+        <v>31.32839506172839</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16199,7 +16333,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>1.8283830129851637</v>
+        <v>1.8593421772776608</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16308,19 +16442,27 @@
       <c r="AI80" s="56">
         <v>20</v>
       </c>
-      <c r="AJ80" s="56"/>
-      <c r="AK80" s="56"/>
-      <c r="AL80" s="56"/>
-      <c r="AM80" s="56"/>
+      <c r="AJ80" s="56">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="AK80" s="56">
+        <v>22.333333333333329</v>
+      </c>
+      <c r="AL80" s="56">
+        <v>21.133333333333329</v>
+      </c>
+      <c r="AM80" s="56">
+        <v>21.866666666666671</v>
+      </c>
       <c r="AN80" s="56"/>
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AQ80" s="71">
         <f t="shared" si="4"/>
-        <v>20.786666666666665</v>
+        <v>20.875862068965517</v>
       </c>
       <c r="AR80" s="71">
         <f>IFERROR(VLOOKUP(A80,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16328,7 +16470,7 @@
       </c>
       <c r="AS80" s="71">
         <f t="shared" si="5"/>
-        <v>1.4800872377361465</v>
+        <v>1.5692826400349986</v>
       </c>
     </row>
     <row r="81" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16440,16 +16582,18 @@
       <c r="AL81" s="56">
         <v>25.2</v>
       </c>
-      <c r="AM81" s="56"/>
+      <c r="AM81" s="56">
+        <v>24.8</v>
+      </c>
       <c r="AN81" s="56"/>
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v>24.209999999999994</v>
+        <v>24.2326923076923</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16457,7 +16601,7 @@
       </c>
       <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v>3.5370093908223765E-2</v>
+        <v>5.8062401600530222E-2</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16575,16 +16719,18 @@
       <c r="AL82" s="56">
         <v>28.266666666666669</v>
       </c>
-      <c r="AM82" s="56"/>
+      <c r="AM82" s="56">
+        <v>25.333333333333329</v>
+      </c>
       <c r="AN82" s="56"/>
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>26.275000000000002</v>
+        <v>26.242528735632188</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16592,7 +16738,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>1.1012775425784227</v>
+        <v>1.0688062782106087</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16850,16 +16996,18 @@
       <c r="AL85" s="56">
         <v>30.5</v>
       </c>
-      <c r="AM85" s="56"/>
+      <c r="AM85" s="56">
+        <v>32.25</v>
+      </c>
       <c r="AN85" s="56"/>
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>30.786842105263155</v>
+        <v>30.859999999999996</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16985,16 +17133,18 @@
       <c r="AL86" s="56">
         <v>30.1</v>
       </c>
-      <c r="AM86" s="56"/>
+      <c r="AM86" s="56">
+        <v>30.25</v>
+      </c>
       <c r="AN86" s="56"/>
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.764285714285709</v>
+        <v>29.781034482758617</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17002,7 +17152,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.1522025527309196</v>
+        <v>1.1689513212038278</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17120,16 +17270,18 @@
       <c r="AL87" s="56">
         <v>30.7</v>
       </c>
-      <c r="AM87" s="56"/>
+      <c r="AM87" s="56">
+        <v>31.95</v>
+      </c>
       <c r="AN87" s="56"/>
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>31.537500000000005</v>
+        <v>31.551724137931043</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17137,7 +17289,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>2.5313100275376144</v>
+        <v>2.5455341654686521</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17255,16 +17407,18 @@
       <c r="AL88" s="56">
         <v>31.35</v>
       </c>
-      <c r="AM88" s="56"/>
+      <c r="AM88" s="56">
+        <v>31.85</v>
+      </c>
       <c r="AN88" s="56"/>
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.178571428571434</v>
+        <v>30.236206896551728</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17272,7 +17426,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>1.4876968125960239</v>
+        <v>1.5453322805763179</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17505,16 +17659,18 @@
       <c r="AL90" s="56">
         <v>33</v>
       </c>
-      <c r="AM90" s="56"/>
+      <c r="AM90" s="56">
+        <v>33.25</v>
+      </c>
       <c r="AN90" s="56"/>
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>31.997916666666669</v>
+        <v>32.048000000000002</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17522,7 +17678,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>2.9628566087540094</v>
+        <v>3.0129399420873426</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17622,16 +17778,18 @@
       <c r="AL91" s="56">
         <v>31.95</v>
       </c>
-      <c r="AM91" s="56"/>
+      <c r="AM91" s="56">
+        <v>29.4</v>
+      </c>
       <c r="AN91" s="56"/>
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v>32.268421052631588</v>
+        <v>32.125000000000007</v>
       </c>
       <c r="AR91" s="71" t="str">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17757,16 +17915,18 @@
       <c r="AL92" s="56">
         <v>16.55</v>
       </c>
-      <c r="AM92" s="56"/>
+      <c r="AM92" s="56">
+        <v>16.600000000000001</v>
+      </c>
       <c r="AN92" s="56"/>
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.465476190476192</v>
+        <v>17.435632183908048</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17774,7 +17934,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.3021321044547207</v>
+        <v>1.2722880978865767</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17892,16 +18052,18 @@
       <c r="AL93" s="56">
         <v>24.466666666666669</v>
       </c>
-      <c r="AM93" s="56"/>
+      <c r="AM93" s="56">
+        <v>24.466666666666669</v>
+      </c>
       <c r="AN93" s="56"/>
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.65</v>
+        <v>23.678160919540229</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17909,7 +18071,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.5405121341303776</v>
+        <v>1.5686730536706079</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18027,16 +18189,18 @@
       <c r="AL94" s="56">
         <v>17.2</v>
       </c>
-      <c r="AM94" s="56"/>
+      <c r="AM94" s="56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="AN94" s="56"/>
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.258035714285718</v>
+        <v>17.304310344827591</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18044,7 +18208,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.1628085683511493</v>
+        <v>1.2090831988930226</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18162,16 +18326,18 @@
       <c r="AL95" s="56">
         <v>14.1</v>
       </c>
-      <c r="AM95" s="56"/>
+      <c r="AM95" s="56">
+        <v>15.45</v>
+      </c>
       <c r="AN95" s="56"/>
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.66607142857143</v>
+        <v>14.693103448275863</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18179,7 +18345,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.0332632924195693</v>
+        <v>1.0602953121240031</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18455,16 +18621,18 @@
       <c r="AL98" s="56">
         <v>12.2</v>
       </c>
-      <c r="AM98" s="56"/>
+      <c r="AM98" s="56">
+        <v>13.8</v>
+      </c>
       <c r="AN98" s="56"/>
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.105357142857143</v>
+        <v>13.129310344827585</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18707,16 +18875,18 @@
       <c r="AL100" s="56">
         <v>15.733333333333331</v>
       </c>
-      <c r="AM100" s="56"/>
+      <c r="AM100" s="56">
+        <v>15.53333333333333</v>
+      </c>
       <c r="AN100" s="56"/>
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v>16.174603174603174</v>
+        <v>16.145454545454545</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18724,7 +18894,7 @@
       </c>
       <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v>1.8652452684951832</v>
+        <v>1.8360966393465539</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18828,16 +18998,18 @@
         <v>13.5</v>
       </c>
       <c r="AL101" s="56"/>
-      <c r="AM101" s="56"/>
+      <c r="AM101" s="56">
+        <v>13.85</v>
+      </c>
       <c r="AN101" s="56"/>
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>13.352380952380955</v>
+        <v>13.375000000000002</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18845,7 +19017,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>1.0199772897696651</v>
+        <v>1.0425963373887122</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18957,16 +19129,18 @@
       <c r="AL102" s="56">
         <v>13.2</v>
       </c>
-      <c r="AM102" s="56"/>
+      <c r="AM102" s="56">
+        <v>13.733333333333331</v>
+      </c>
       <c r="AN102" s="56"/>
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>13.032000000000004</v>
+        <v>13.058974358974362</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18974,7 +19148,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>1.7850046306141127</v>
+        <v>1.8119789895884715</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19244,16 +19418,18 @@
       <c r="AL105" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="AM105" s="56"/>
+      <c r="AM105" s="56">
+        <v>19.399999999999999</v>
+      </c>
       <c r="AN105" s="56"/>
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.168000000000003</v>
+        <v>18.215384615384615</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19261,7 +19437,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.1234624915237319</v>
+        <v>1.1708471069083437</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19434,16 +19610,18 @@
       <c r="AL107" s="56">
         <v>13.133333333333329</v>
       </c>
-      <c r="AM107" s="56"/>
+      <c r="AM107" s="56">
+        <v>13.2</v>
+      </c>
       <c r="AN107" s="56"/>
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ107" s="71">
         <f t="shared" si="4"/>
-        <v>14.837500000000002</v>
+        <v>14.741176470588236</v>
       </c>
       <c r="AR107" s="71">
         <f>IFERROR(VLOOKUP(A107,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19451,7 +19629,7 @@
       </c>
       <c r="AS107" s="71">
         <f t="shared" si="5"/>
-        <v>1.4171833930705322</v>
+        <v>1.3208598636587663</v>
       </c>
     </row>
     <row r="108" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19569,16 +19747,18 @@
       <c r="AL108" s="56">
         <v>13.85</v>
       </c>
-      <c r="AM108" s="56"/>
+      <c r="AM108" s="56">
+        <v>14.7</v>
+      </c>
       <c r="AN108" s="56"/>
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>14.205357142857144</v>
+        <v>14.222413793103449</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19586,7 +19766,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>-2.3675771874666296E-2</v>
+        <v>-6.619121628361313E-3</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19704,16 +19884,18 @@
       <c r="AL109" s="56">
         <v>14.95</v>
       </c>
-      <c r="AM109" s="56"/>
+      <c r="AM109" s="56">
+        <v>15.6</v>
+      </c>
       <c r="AN109" s="56"/>
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.571428571428569</v>
+        <v>14.606896551724137</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19721,7 +19903,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.85766548392077979</v>
+        <v>0.89313346421634776</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19839,16 +20021,18 @@
       <c r="AL110" s="56">
         <v>17.93333333333333</v>
       </c>
-      <c r="AM110" s="56"/>
+      <c r="AM110" s="56">
+        <v>17.333333333333329</v>
+      </c>
       <c r="AN110" s="56"/>
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.542857142857137</v>
+        <v>17.535632183908039</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19856,7 +20040,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.60789510439024852</v>
+        <v>0.60067014544114983</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19974,16 +20158,18 @@
       <c r="AL111" s="56">
         <v>15.133333333333329</v>
       </c>
-      <c r="AM111" s="56"/>
+      <c r="AM111" s="56">
+        <v>17</v>
+      </c>
       <c r="AN111" s="56"/>
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.894047619047623</v>
+        <v>15.93218390804598</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19991,7 +20177,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.39168409547443339</v>
+        <v>0.42982038447279081</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20109,16 +20295,18 @@
       <c r="AL112" s="56">
         <v>18.266666666666669</v>
       </c>
-      <c r="AM112" s="56"/>
+      <c r="AM112" s="56">
+        <v>17.133333333333329</v>
+      </c>
       <c r="AN112" s="56"/>
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>17.847619047619045</v>
+        <v>17.822988505747123</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20126,7 +20314,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.4679227865169651</v>
+        <v>1.4432922446450434</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20343,12 +20531,14 @@
       <c r="AL114" s="56">
         <v>22.666666666666671</v>
       </c>
-      <c r="AM114" s="56"/>
+      <c r="AM114" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="AN114" s="56"/>
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -20478,16 +20668,18 @@
       <c r="AL115" s="56">
         <v>28.25</v>
       </c>
-      <c r="AM115" s="56"/>
+      <c r="AM115" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AN115" s="56"/>
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.33660714285714</v>
+        <v>26.335344827586205</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20495,7 +20687,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.4921271651041188</v>
+        <v>0.49086484983318357</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20609,16 +20801,18 @@
       <c r="AL116" s="56">
         <v>19.266666666666669</v>
       </c>
-      <c r="AM116" s="56"/>
+      <c r="AM116" s="56">
+        <v>19.8</v>
+      </c>
       <c r="AN116" s="56"/>
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.251282051282054</v>
+        <v>19.271604938271608</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20626,7 +20820,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.85477688494123427</v>
+        <v>0.87509977193078825</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20744,16 +20938,18 @@
       <c r="AL117" s="56">
         <v>28.2</v>
       </c>
-      <c r="AM117" s="56"/>
+      <c r="AM117" s="56">
+        <v>27</v>
+      </c>
       <c r="AN117" s="56"/>
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>26.295238095238098</v>
+        <v>26.31954022988506</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20761,7 +20957,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.9263984895033488</v>
+        <v>0.95070062415031131</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20879,16 +21075,18 @@
       <c r="AL118" s="56">
         <v>30.4</v>
       </c>
-      <c r="AM118" s="56"/>
+      <c r="AM118" s="56">
+        <v>29.466666666666669</v>
+      </c>
       <c r="AN118" s="56"/>
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ118" s="71">
         <f t="shared" si="4"/>
-        <v>28.785714285714285</v>
+        <v>28.809195402298851</v>
       </c>
       <c r="AR118" s="71">
         <f>IFERROR(VLOOKUP(A118,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20896,7 +21094,7 @@
       </c>
       <c r="AS118" s="71">
         <f t="shared" si="5"/>
-        <v>3.0324347158218252</v>
+        <v>3.0559158324063915</v>
       </c>
     </row>
     <row r="119" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21014,16 +21212,18 @@
       <c r="AL119" s="56">
         <v>23.2</v>
       </c>
-      <c r="AM119" s="56"/>
+      <c r="AM119" s="56">
+        <v>24.666666666666671</v>
+      </c>
       <c r="AN119" s="56"/>
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ119" s="71">
         <f t="shared" si="4"/>
-        <v>23.609523809523811</v>
+        <v>23.645977011494253</v>
       </c>
       <c r="AR119" s="71">
         <f>IFERROR(VLOOKUP(A119,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21031,7 +21231,7 @@
       </c>
       <c r="AS119" s="71">
         <f t="shared" si="5"/>
-        <v>1.8810829493088015</v>
+        <v>1.9175361512792435</v>
       </c>
     </row>
     <row r="120" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21329,16 +21529,18 @@
       <c r="AL122" s="56">
         <v>11.8</v>
       </c>
-      <c r="AM122" s="56"/>
+      <c r="AM122" s="56">
+        <v>12.33333333333333</v>
+      </c>
       <c r="AN122" s="56"/>
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.051190476190476</v>
+        <v>12.060919540229884</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21346,7 +21548,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.7484334802201964</v>
+        <v>1.7581625442596049</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21538,17 +21740,19 @@
       <c r="AK124" s="56">
         <v>16</v>
       </c>
-      <c r="AL124" s="56"/>
+      <c r="AL124" s="56">
+        <v>15.8</v>
+      </c>
       <c r="AM124" s="56"/>
       <c r="AN124" s="56"/>
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ124" s="71">
         <f t="shared" si="4"/>
-        <v>16.005128205128205</v>
+        <v>15.997530864197531</v>
       </c>
       <c r="AR124" s="71">
         <f>IFERROR(VLOOKUP(A124,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21556,7 +21760,7 @@
       </c>
       <c r="AS124" s="71">
         <f t="shared" si="5"/>
-        <v>0.95606924558469508</v>
+        <v>0.94847190465402065</v>
       </c>
     </row>
     <row r="125" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21737,16 +21941,18 @@
         <v>11.46666666666667</v>
       </c>
       <c r="AL126" s="56"/>
-      <c r="AM126" s="56"/>
+      <c r="AM126" s="56">
+        <v>10.6</v>
+      </c>
       <c r="AN126" s="56"/>
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ126" s="71">
         <f t="shared" si="4"/>
-        <v>11.873333333333331</v>
+        <v>11.81269841269841</v>
       </c>
       <c r="AR126" s="71">
         <f>IFERROR(VLOOKUP(A126,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21754,7 +21960,7 @@
       </c>
       <c r="AS126" s="71">
         <f t="shared" si="5"/>
-        <v>1.160887117269592</v>
+        <v>1.1002521966346706</v>
       </c>
     </row>
     <row r="127" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22244,16 +22450,18 @@
       <c r="AL131" s="56">
         <v>18</v>
       </c>
-      <c r="AM131" s="56"/>
+      <c r="AM131" s="56">
+        <v>18.8</v>
+      </c>
       <c r="AN131" s="56"/>
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.296428571428574</v>
+        <v>18.313793103448276</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22261,7 +22469,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.5035315725246257</v>
+        <v>1.5208961045443274</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22458,16 +22666,18 @@
       <c r="AL133" s="56">
         <v>13.43333333333333</v>
       </c>
-      <c r="AM133" s="56"/>
+      <c r="AM133" s="56">
+        <v>13.66666666666667</v>
+      </c>
       <c r="AN133" s="56"/>
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>13.869047619047617</v>
+        <v>13.86206896551724</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22475,7 +22685,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.233707844393777</v>
+        <v>1.2267291908634004</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22593,16 +22803,18 @@
       <c r="AL134" s="56">
         <v>17.466666666666669</v>
       </c>
-      <c r="AM134" s="56"/>
+      <c r="AM134" s="56">
+        <v>17.466666666666669</v>
+      </c>
       <c r="AN134" s="56"/>
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>17.783333333333331</v>
+        <v>17.772413793103446</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22610,7 +22822,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.2011544909496621</v>
+        <v>2.1902349507197769</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22728,16 +22940,18 @@
       <c r="AL135" s="56">
         <v>21.25</v>
       </c>
-      <c r="AM135" s="56"/>
+      <c r="AM135" s="56">
+        <v>21.45</v>
+      </c>
       <c r="AN135" s="56"/>
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>20.623214285714287</v>
+        <v>20.651724137931037</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22745,7 +22959,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>1.9413336483091577</v>
+        <v>1.9698435005259078</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22859,16 +23073,18 @@
       </c>
       <c r="AK136" s="56"/>
       <c r="AL136" s="56"/>
-      <c r="AM136" s="56"/>
+      <c r="AM136" s="56">
+        <v>9.6</v>
+      </c>
       <c r="AN136" s="56"/>
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ136" s="71">
         <f t="shared" si="7"/>
-        <v>11.138461538461534</v>
+        <v>11.081481481481479</v>
       </c>
       <c r="AR136" s="71">
         <f>IFERROR(VLOOKUP(A136,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22876,7 +23092,7 @@
       </c>
       <c r="AS136" s="71">
         <f t="shared" si="8"/>
-        <v>0.28081146430507431</v>
+        <v>0.22383140732501872</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23073,16 +23289,18 @@
       <c r="AL138" s="56">
         <v>22.533333333333331</v>
       </c>
-      <c r="AM138" s="56"/>
+      <c r="AM138" s="56">
+        <v>21.8</v>
+      </c>
       <c r="AN138" s="56"/>
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>22.171428571428571</v>
+        <v>22.158620689655169</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23090,7 +23308,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.1612074740801717</v>
+        <v>2.1483995923067702</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23208,16 +23426,18 @@
       <c r="AL139" s="56">
         <v>13.35</v>
       </c>
-      <c r="AM139" s="56"/>
+      <c r="AM139" s="56">
+        <v>13.6</v>
+      </c>
       <c r="AN139" s="56"/>
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>13.991964285714285</v>
+        <v>13.978448275862069</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23225,7 +23445,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.0877465128802761</v>
+        <v>1.0742305030280601</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23343,16 +23563,18 @@
       <c r="AL140" s="56">
         <v>15.15</v>
       </c>
-      <c r="AM140" s="56"/>
+      <c r="AM140" s="56">
+        <v>15.95</v>
+      </c>
       <c r="AN140" s="56"/>
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.341071428571428</v>
+        <v>16.327586206896552</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23360,7 +23582,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.74672085680150779</v>
+        <v>0.73323563512663092</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23478,16 +23700,18 @@
       <c r="AL141" s="56">
         <v>13.53333333333333</v>
       </c>
-      <c r="AM141" s="56"/>
+      <c r="AM141" s="56">
+        <v>12.133333333333329</v>
+      </c>
       <c r="AN141" s="56"/>
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.430952380952382</v>
+        <v>13.386206896551725</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23495,7 +23719,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.4169229841143327</v>
+        <v>1.3721774997136755</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23611,16 +23835,18 @@
       <c r="AL142" s="56">
         <v>11</v>
       </c>
-      <c r="AM142" s="56"/>
+      <c r="AM142" s="56">
+        <v>10.75</v>
+      </c>
       <c r="AN142" s="56"/>
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>11.579629629629631</v>
+        <v>11.55</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23628,7 +23854,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.05064365314783</v>
+        <v>1.0210140235181999</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23746,16 +23972,18 @@
       <c r="AL143" s="56">
         <v>28.466666666666669</v>
       </c>
-      <c r="AM143" s="56"/>
+      <c r="AM143" s="56">
+        <v>28.13333333333334</v>
+      </c>
       <c r="AN143" s="56"/>
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.704761904761906</v>
+        <v>27.719540229885059</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23763,7 +23991,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>1.842821812596025</v>
+        <v>1.857600137719178</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24012,16 +24240,18 @@
       <c r="AL145" s="56">
         <v>20.466666666666669</v>
       </c>
-      <c r="AM145" s="56"/>
+      <c r="AM145" s="56">
+        <v>20.466666666666669</v>
+      </c>
       <c r="AN145" s="56"/>
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>19.50714285714286</v>
+        <v>19.540229885057474</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24029,7 +24259,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>0.46512632264473908</v>
+        <v>0.49821335055935378</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24144,17 +24374,21 @@
       <c r="AK146" s="56">
         <v>29.13333333333334</v>
       </c>
-      <c r="AL146" s="56"/>
-      <c r="AM146" s="56"/>
+      <c r="AL146" s="56">
+        <v>30.8</v>
+      </c>
+      <c r="AM146" s="56">
+        <v>31.933333333333341</v>
+      </c>
       <c r="AN146" s="56"/>
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v>29.869135802469131</v>
+        <v>29.972413793103446</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24162,7 +24396,7 @@
       </c>
       <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v>1.1119362646719004</v>
+        <v>1.2152142553062149</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24280,16 +24514,18 @@
       <c r="AL147" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="AM147" s="56"/>
+      <c r="AM147" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AN147" s="56"/>
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.238095238095241</v>
+        <v>25.250574712643683</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24297,7 +24533,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.7340377462318806</v>
+        <v>1.7465172207803228</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24411,16 +24647,18 @@
       <c r="AL148" s="56">
         <v>31.6</v>
       </c>
-      <c r="AM148" s="56"/>
+      <c r="AM148" s="56">
+        <v>31.666666666666671</v>
+      </c>
       <c r="AN148" s="56"/>
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.355128205128203</v>
+        <v>30.403703703703698</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24428,7 +24666,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.7135969742734218</v>
+        <v>1.762172472848917</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24546,16 +24784,18 @@
       <c r="AL149" s="56">
         <v>23.666666666666671</v>
       </c>
-      <c r="AM149" s="56"/>
+      <c r="AM149" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AN149" s="56"/>
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.507142857142856</v>
+        <v>23.565517241379311</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24563,7 +24803,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.6310750841900052</v>
+        <v>1.68944946842646</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24756,16 +24996,18 @@
       <c r="AL151" s="56">
         <v>23.8</v>
       </c>
-      <c r="AM151" s="56"/>
+      <c r="AM151" s="56">
+        <v>25.4</v>
+      </c>
       <c r="AN151" s="56"/>
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ151" s="71">
         <f t="shared" si="7"/>
-        <v>23.256410256410252</v>
+        <v>23.335802469135796</v>
       </c>
       <c r="AR151" s="71">
         <f>IFERROR(VLOOKUP(A151,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24773,7 +25015,7 @@
       </c>
       <c r="AS151" s="71">
         <f t="shared" si="8"/>
-        <v>1.4438229777896119</v>
+        <v>1.5232151905151561</v>
       </c>
     </row>
     <row r="152" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25049,16 +25291,18 @@
       <c r="AL154" s="56">
         <v>20.45</v>
       </c>
-      <c r="AM154" s="56"/>
+      <c r="AM154" s="56">
+        <v>20.65</v>
+      </c>
       <c r="AN154" s="56"/>
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>20.453571428571429</v>
+        <v>20.460344827586209</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25066,7 +25310,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>0.93995067417649025</v>
+        <v>0.94672407319126961</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25184,16 +25428,18 @@
       <c r="AL155" s="56">
         <v>29.666666666666671</v>
       </c>
-      <c r="AM155" s="56"/>
+      <c r="AM155" s="56">
+        <v>30</v>
+      </c>
       <c r="AN155" s="56"/>
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>28.859523809523807</v>
+        <v>28.898850574712643</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25201,7 +25447,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.136737248668009</v>
+        <v>1.1760640138568448</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25387,17 +25633,21 @@
       <c r="AK157" s="56">
         <v>28.4</v>
       </c>
-      <c r="AL157" s="56"/>
-      <c r="AM157" s="56"/>
+      <c r="AL157" s="56">
+        <v>29.333333333333329</v>
+      </c>
+      <c r="AM157" s="56">
+        <v>30</v>
+      </c>
       <c r="AN157" s="56"/>
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ157" s="71">
         <f t="shared" si="7"/>
-        <v>29.275362318840585</v>
+        <v>29.306666666666676</v>
       </c>
       <c r="AR157" s="71">
         <f>IFERROR(VLOOKUP(A157,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25405,7 +25655,7 @@
       </c>
       <c r="AS157" s="71">
         <f t="shared" si="8"/>
-        <v>1.6909348222311849</v>
+        <v>1.722239170057275</v>
       </c>
     </row>
     <row r="158" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25517,16 +25767,18 @@
       <c r="AL158" s="56">
         <v>31</v>
       </c>
-      <c r="AM158" s="56"/>
+      <c r="AM158" s="56">
+        <v>31.8</v>
+      </c>
       <c r="AN158" s="56"/>
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>30.03733333333334</v>
+        <v>30.10512820512821</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25534,7 +25786,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>2.0189211662531399</v>
+        <v>2.0867160380480101</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25646,16 +25898,18 @@
       <c r="AL159" s="56">
         <v>20.2</v>
       </c>
-      <c r="AM159" s="56"/>
+      <c r="AM159" s="56">
+        <v>21.266666666666669</v>
+      </c>
       <c r="AN159" s="56"/>
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.281333333333336</v>
+        <v>20.319230769230771</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25663,7 +25917,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.2903962186429361</v>
+        <v>1.3282936545403707</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25779,16 +26033,18 @@
       <c r="AL160" s="56">
         <v>27.8</v>
       </c>
-      <c r="AM160" s="56"/>
+      <c r="AM160" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="AN160" s="56"/>
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.056790123456796</v>
+        <v>27.042857142857148</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25890,16 +26146,18 @@
       <c r="AL161" s="56">
         <v>19.866666666666671</v>
       </c>
-      <c r="AM161" s="56"/>
+      <c r="AM161" s="56">
+        <v>21.4</v>
+      </c>
       <c r="AN161" s="56"/>
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ161" s="71">
         <f t="shared" si="7"/>
-        <v>19.183333333333337</v>
+        <v>19.313725490196081</v>
       </c>
       <c r="AR161" s="71">
         <f>IFERROR(VLOOKUP(A161,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25907,7 +26165,7 @@
       </c>
       <c r="AS161" s="71">
         <f t="shared" si="8"/>
-        <v>1.6234532676842868</v>
+        <v>1.7538454245470305</v>
       </c>
     </row>
     <row r="162" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26025,16 +26283,18 @@
       <c r="AL162" s="56">
         <v>29.06666666666667</v>
       </c>
-      <c r="AM162" s="56"/>
+      <c r="AM162" s="56">
+        <v>29.866666666666671</v>
+      </c>
       <c r="AN162" s="56"/>
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>28.878571428571437</v>
+        <v>28.912643678160929</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26042,7 +26302,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.30503404069715856</v>
+        <v>0.33910629028665085</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26160,16 +26420,18 @@
       <c r="AL163" s="56">
         <v>21.533333333333331</v>
       </c>
-      <c r="AM163" s="56"/>
+      <c r="AM163" s="56">
+        <v>21.6</v>
+      </c>
       <c r="AN163" s="56"/>
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.416666666666664</v>
+        <v>21.422988505747124</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26177,7 +26439,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.16724285106608505</v>
+        <v>0.17356469014654508</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26295,16 +26557,18 @@
       <c r="AL164" s="56">
         <v>25.15</v>
       </c>
-      <c r="AM164" s="56"/>
+      <c r="AM164" s="56">
+        <v>25.85</v>
+      </c>
       <c r="AN164" s="56"/>
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.38214285714286</v>
+        <v>25.398275862068967</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26312,7 +26576,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.5842152479827796</v>
+        <v>1.600348252908887</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26505,16 +26769,18 @@
       <c r="AL166" s="56">
         <v>15.133333333333329</v>
       </c>
-      <c r="AM166" s="56"/>
+      <c r="AM166" s="56">
+        <v>15.46666666666667</v>
+      </c>
       <c r="AN166" s="56"/>
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.730769230769234</v>
+        <v>14.758024691358028</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26522,7 +26788,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.1322996967190928</v>
+        <v>1.1595551573078868</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26636,16 +26902,18 @@
       <c r="AL167" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="AM167" s="56"/>
+      <c r="AM167" s="56">
+        <v>21.4</v>
+      </c>
       <c r="AN167" s="56"/>
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.661538461538463</v>
+        <v>20.68888888888889</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26653,7 +26921,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.6259706519278225</v>
+        <v>1.6533210792782498</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26767,16 +27035,18 @@
       <c r="AL168" s="56">
         <v>29.1</v>
       </c>
-      <c r="AM168" s="56"/>
+      <c r="AM168" s="56">
+        <v>28.1</v>
+      </c>
       <c r="AN168" s="56"/>
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.826923076923087</v>
+        <v>27.837037037037046</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26784,7 +27054,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.7610586108565087</v>
+        <v>1.7711725709704673</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26902,16 +27172,18 @@
       <c r="AL169" s="56">
         <v>9.9</v>
       </c>
-      <c r="AM169" s="56"/>
+      <c r="AM169" s="56">
+        <v>9</v>
+      </c>
       <c r="AN169" s="56"/>
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>9.0196428571428573</v>
+        <v>9.0189655172413783</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26919,7 +27191,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.47751857578832002</v>
+        <v>0.47684123588684102</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27021,16 +27293,18 @@
       <c r="AL170" s="56">
         <v>27.266666666666669</v>
       </c>
-      <c r="AM170" s="56"/>
+      <c r="AM170" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="AN170" s="56"/>
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v>24.93</v>
+        <v>25.098412698412695</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27038,7 +27312,7 @@
       </c>
       <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v>0.83937605813752825</v>
+        <v>1.007788756550223</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27154,16 +27428,18 @@
       <c r="AL171" s="56">
         <v>21.6</v>
       </c>
-      <c r="AM171" s="56"/>
+      <c r="AM171" s="56">
+        <v>21.4</v>
+      </c>
       <c r="AN171" s="56"/>
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>20.74074074074074</v>
+        <v>20.764285714285712</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27171,7 +27447,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.8118147184888223</v>
+        <v>1.8353596920337942</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27285,16 +27561,18 @@
       <c r="AL172" s="56">
         <v>27.35</v>
       </c>
-      <c r="AM172" s="56"/>
+      <c r="AM172" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AN172" s="56"/>
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.734615384615385</v>
+        <v>25.755555555555556</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27302,7 +27580,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.2959870161035063</v>
+        <v>1.3169271870436781</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27420,16 +27698,18 @@
       <c r="AL173" s="56">
         <v>25.45</v>
       </c>
-      <c r="AM173" s="56"/>
+      <c r="AM173" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AN173" s="56"/>
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.112797619047626</v>
+        <v>25.150287356321847</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27437,7 +27717,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.0583890168970953</v>
+        <v>1.0958787541713164</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27553,16 +27833,18 @@
       <c r="AL174" s="56">
         <v>14.2</v>
       </c>
-      <c r="AM174" s="56"/>
+      <c r="AM174" s="56">
+        <v>12.733333333333331</v>
+      </c>
       <c r="AN174" s="56"/>
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ174" s="71">
         <f t="shared" si="7"/>
-        <v>13.933333333333335</v>
+        <v>13.890476190476193</v>
       </c>
       <c r="AR174" s="71">
         <f>IFERROR(VLOOKUP(A174,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27570,7 +27852,7 @@
       </c>
       <c r="AS174" s="71">
         <f t="shared" si="8"/>
-        <v>1.8725814756614749</v>
+        <v>1.8297243328043322</v>
       </c>
     </row>
     <row r="175" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27957,16 +28239,18 @@
       <c r="AL178" s="56">
         <v>26.733333333333331</v>
       </c>
-      <c r="AM178" s="56"/>
+      <c r="AM178" s="56">
+        <v>25.866666666666671</v>
+      </c>
       <c r="AN178" s="56"/>
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>25.202898550724637</v>
+        <v>25.230555555555554</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27974,7 +28258,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.65061820384574531</v>
+        <v>0.6782752086766628</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28084,16 +28368,18 @@
       <c r="AL179" s="56">
         <v>19.2</v>
       </c>
-      <c r="AM179" s="56"/>
+      <c r="AM179" s="56">
+        <v>19.95</v>
+      </c>
       <c r="AN179" s="56"/>
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>18.554166666666664</v>
+        <v>18.61</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28101,7 +28387,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>0.9665829831500119</v>
+        <v>1.0224163164833477</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28298,16 +28584,18 @@
       <c r="AL181" s="56">
         <v>32.266666666666673</v>
       </c>
-      <c r="AM181" s="56"/>
+      <c r="AM181" s="56">
+        <v>29.4</v>
+      </c>
       <c r="AN181" s="56"/>
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ181" s="71">
         <f t="shared" si="7"/>
-        <v>31.011904761904759</v>
+        <v>30.956321839080456</v>
       </c>
       <c r="AR181" s="71">
         <f>IFERROR(VLOOKUP(A181,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28315,7 +28603,7 @@
       </c>
       <c r="AS181" s="71">
         <f t="shared" si="8"/>
-        <v>2.4786683743349478</v>
+        <v>2.4230854515106444</v>
       </c>
     </row>
     <row r="182" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28591,16 +28879,18 @@
       <c r="AL184" s="56">
         <v>29.36666666666666</v>
       </c>
-      <c r="AM184" s="56"/>
+      <c r="AM184" s="56">
+        <v>28.066666666666659</v>
+      </c>
       <c r="AN184" s="56"/>
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>28.144047619047623</v>
+        <v>28.141379310344828</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28608,7 +28898,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.5056764014306339</v>
+        <v>1.5030080927278391</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28718,16 +29008,18 @@
       <c r="AL185" s="56">
         <v>29.06666666666667</v>
       </c>
-      <c r="AM185" s="56"/>
+      <c r="AM185" s="56">
+        <v>28.733333333333331</v>
+      </c>
       <c r="AN185" s="56"/>
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ185" s="71">
         <f t="shared" si="7"/>
-        <v>28.938888888888886</v>
+        <v>28.930666666666667</v>
       </c>
       <c r="AR185" s="71">
         <f>IFERROR(VLOOKUP(A185,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28735,7 +29027,7 @@
       </c>
       <c r="AS185" s="71">
         <f t="shared" si="8"/>
-        <v>1.3302566038775154</v>
+        <v>1.3220343816552962</v>
       </c>
     </row>
     <row r="186" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29011,16 +29303,18 @@
       <c r="AL188" s="56">
         <v>16.93333333333333</v>
       </c>
-      <c r="AM188" s="56"/>
+      <c r="AM188" s="56">
+        <v>17.600000000000001</v>
+      </c>
       <c r="AN188" s="56"/>
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>17.288095238095242</v>
+        <v>17.298850574712649</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29028,7 +29322,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.2925032485635111</v>
+        <v>1.3032585851809184</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29132,16 +29426,18 @@
         <v>32.133333333333333</v>
       </c>
       <c r="AL189" s="56"/>
-      <c r="AM189" s="56"/>
+      <c r="AM189" s="56">
+        <v>32.133333333333333</v>
+      </c>
       <c r="AN189" s="56"/>
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>31.987301587301594</v>
+        <v>31.993939393939399</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29149,7 +29445,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>2.1357172292488045</v>
+        <v>2.1423550358866095</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29267,16 +29563,18 @@
       <c r="AL190" s="56">
         <v>30.333333333333329</v>
       </c>
-      <c r="AM190" s="56"/>
+      <c r="AM190" s="56">
+        <v>29.466666666666669</v>
+      </c>
       <c r="AN190" s="56"/>
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>30.530952380952382</v>
+        <v>30.494252873563219</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29284,7 +29582,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.6144287194699132</v>
+        <v>1.5777292120807509</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29402,16 +29700,18 @@
       <c r="AL191" s="56">
         <v>18.75</v>
       </c>
-      <c r="AM191" s="56"/>
+      <c r="AM191" s="56">
+        <v>18.649999999999999</v>
+      </c>
       <c r="AN191" s="56"/>
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.55535714285714</v>
+        <v>18.558620689655172</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29419,7 +29719,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.1681381281965315</v>
+        <v>1.1714016749945628</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29537,16 +29837,18 @@
       <c r="AL192" s="56">
         <v>27.2</v>
       </c>
-      <c r="AM192" s="56"/>
+      <c r="AM192" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AN192" s="56"/>
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.230952380952395</v>
+        <v>26.236781609195415</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29554,7 +29856,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.98644520013422365</v>
+        <v>0.99227442837724311</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29666,16 +29968,18 @@
       <c r="AL193" s="56">
         <v>28.8</v>
       </c>
-      <c r="AM193" s="56"/>
+      <c r="AM193" s="56">
+        <v>29.55</v>
+      </c>
       <c r="AN193" s="56"/>
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>27.187999999999999</v>
+        <v>27.27884615384615</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29683,7 +29987,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>0.83523045999082868</v>
+        <v>0.92607661383697959</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29801,16 +30105,18 @@
       <c r="AL194" s="56">
         <v>22.8</v>
       </c>
-      <c r="AM194" s="56"/>
+      <c r="AM194" s="56">
+        <v>21.8</v>
+      </c>
       <c r="AN194" s="56"/>
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.223809523809525</v>
+        <v>21.243678160919536</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29818,7 +30124,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-0.38385227324890536</v>
+        <v>-0.36398363613889373</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29936,16 +30242,18 @@
       <c r="AL195" s="56">
         <v>26.86666666666666</v>
       </c>
-      <c r="AM195" s="56"/>
+      <c r="AM195" s="56">
+        <v>27.133333333333329</v>
+      </c>
       <c r="AN195" s="56"/>
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>27.547619047619047</v>
+        <v>27.533333333333335</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29953,7 +30261,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>1.8601308379092885</v>
+        <v>1.845845123623576</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30071,16 +30379,18 @@
       <c r="AL196" s="56">
         <v>21.533333333333331</v>
       </c>
-      <c r="AM196" s="56"/>
+      <c r="AM196" s="56">
+        <v>21.8</v>
+      </c>
       <c r="AN196" s="56"/>
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>22.050000000000004</v>
+        <v>22.04137931034483</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30088,7 +30398,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>1.826243528474734</v>
+        <v>1.8176228388195597</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30206,16 +30516,18 @@
       <c r="AL197" s="56">
         <v>26.6</v>
       </c>
-      <c r="AM197" s="56"/>
+      <c r="AM197" s="56">
+        <v>26.93333333333333</v>
+      </c>
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.935714285714287</v>
+        <v>25.970114942528735</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30223,7 +30535,7 @@
       </c>
       <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.8083312845437582</v>
+        <v>1.8427319413582062</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30341,16 +30653,18 @@
       <c r="AL198" s="56">
         <v>21.8</v>
       </c>
-      <c r="AM198" s="56"/>
+      <c r="AM198" s="56">
+        <v>21.55</v>
+      </c>
       <c r="AN198" s="56"/>
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.603571428571424</v>
+        <v>21.601724137931029</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30476,16 +30790,18 @@
       <c r="AL199" s="56">
         <v>16.399999999999999</v>
       </c>
-      <c r="AM199" s="56"/>
+      <c r="AM199" s="56">
+        <v>16.600000000000001</v>
+      </c>
       <c r="AN199" s="56"/>
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.569047619047616</v>
+        <v>16.570114942528736</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30493,7 +30809,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.78138721285642632</v>
+        <v>0.78245453633754636</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30611,16 +30927,18 @@
       <c r="AL200" s="56">
         <v>14.15</v>
       </c>
-      <c r="AM200" s="56"/>
+      <c r="AM200" s="56">
+        <v>14.65</v>
+      </c>
       <c r="AN200" s="56"/>
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.625</v>
+        <v>14.625862068965516</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30628,7 +30946,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.2593875322163601</v>
+        <v>1.2602496011818758</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30746,16 +31064,18 @@
       <c r="AL201" s="56">
         <v>26.85</v>
       </c>
-      <c r="AM201" s="56"/>
+      <c r="AM201" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AN201" s="56"/>
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>27.074999999999996</v>
+        <v>27.082758620689649</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30763,7 +31083,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>1.5374707316691456</v>
+        <v>1.545229352358799</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30862,17 +31182,19 @@
       <c r="AK202" s="56">
         <v>12.5</v>
       </c>
-      <c r="AL202" s="56"/>
+      <c r="AL202" s="56">
+        <v>11.8</v>
+      </c>
       <c r="AM202" s="56"/>
       <c r="AN202" s="56"/>
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ202" s="71">
         <f t="shared" si="10"/>
-        <v>13.45</v>
+        <v>13.367499999999998</v>
       </c>
       <c r="AR202" s="71">
         <f>IFERROR(VLOOKUP(A202,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30880,7 +31202,7 @@
       </c>
       <c r="AS202" s="71">
         <f t="shared" si="11"/>
-        <v>0.64643604149607903</v>
+        <v>0.56393604149607768</v>
       </c>
     </row>
     <row r="203" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31224,16 +31546,18 @@
       <c r="AL205" s="56">
         <v>14.55</v>
       </c>
-      <c r="AM205" s="56"/>
+      <c r="AM205" s="56">
+        <v>14.85</v>
+      </c>
       <c r="AN205" s="56"/>
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>14.5375</v>
+        <v>14.548275862068966</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31241,7 +31565,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.1226058831823291</v>
+        <v>1.1333817452512953</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31462,16 +31786,18 @@
       <c r="AL207" s="56">
         <v>13.2</v>
       </c>
-      <c r="AM207" s="56"/>
+      <c r="AM207" s="56">
+        <v>14.266666666666669</v>
+      </c>
       <c r="AN207" s="56"/>
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v>14.228070175438592</v>
+        <v>14.229999999999995</v>
       </c>
       <c r="AR207" s="71">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31479,7 +31805,7 @@
       </c>
       <c r="AS207" s="71">
         <f t="shared" si="11"/>
-        <v>0.66729437037587225</v>
+        <v>0.66922419493727503</v>
       </c>
     </row>
     <row r="208" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31595,16 +31921,18 @@
       <c r="AL208" s="56">
         <v>14</v>
       </c>
-      <c r="AM208" s="56"/>
+      <c r="AM208" s="56">
+        <v>14.4</v>
+      </c>
       <c r="AN208" s="56"/>
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>14.174074074074072</v>
+        <v>14.182142857142853</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31730,16 +32058,18 @@
       <c r="AL209" s="56">
         <v>11.25</v>
       </c>
-      <c r="AM209" s="56"/>
+      <c r="AM209" s="56">
+        <v>10.75</v>
+      </c>
       <c r="AN209" s="56"/>
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.089285714285717</v>
+        <v>11.077586206896553</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -32127,16 +32457,18 @@
       <c r="AL212" s="56">
         <v>27.75</v>
       </c>
-      <c r="AM212" s="56"/>
+      <c r="AM212" s="56">
+        <v>27.55</v>
+      </c>
       <c r="AN212" s="56"/>
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v>25.753571428571416</v>
+        <v>25.815517241379297</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
